--- a/TestData/TMTI0027301_VerifyTheIndustryNameIsUpdatedOnContactDetailPage.xlsx
+++ b/TestData/TMTI0027301_VerifyTheIndustryNameIsUpdatedOnContactDetailPage.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEC1F0E-5D41-413C-83DA-B9CD1569359C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D0DBBA-4BFC-4D91-B8BE-EB02568375A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
-    <sheet name="IndustryType" sheetId="1" r:id="rId2"/>
-    <sheet name="Contact" sheetId="9" r:id="rId3"/>
+    <sheet name="AppName" sheetId="10" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="11" r:id="rId3"/>
+    <sheet name="IndustryType" sheetId="1" r:id="rId4"/>
+    <sheet name="Contact" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,20 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>StdUser</t>
   </si>
   <si>
-    <t>CaoUser</t>
-  </si>
-  <si>
-    <t>Emre Abale</t>
-  </si>
-  <si>
-    <t>Meissa Lee</t>
-  </si>
-  <si>
     <t>IndustryGroupType</t>
   </si>
   <si>
@@ -50,19 +43,34 @@
     <t>CompanyName</t>
   </si>
   <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
     <t>Houlihan Lokey - NY</t>
   </si>
   <si>
-    <t>Oscar</t>
-  </si>
-  <si>
-    <t>Aarts</t>
+    <t>James Craven</t>
+  </si>
+  <si>
+    <t>CF Financial User</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Contacts</t>
+  </si>
+  <si>
+    <t>Oscar Aarts</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -794,26 +802,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -822,21 +830,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B18119-9CFC-474A-81F9-3B1B069FBF20}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBC5BB5-11B1-4E0D-8EFF-41776B7BAD84}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -846,36 +897,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8C51AF-DEAB-411D-999C-276DD13EBE95}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
